--- a/demo-runs/2026-10-17/demo3_dcf_valuation/GOOGL_DCF_Valuation.xlsx
+++ b/demo-runs/2026-10-17/demo3_dcf_valuation/GOOGL_DCF_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h_min\repos\SNU_Agentic_AI_Lecture\demo-runs\2026-10-17\demo3_dcf_valuation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB710F5D-DD84-4A03-BD22-12E4C1F6C320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D442921-DFDB-4027-A51D-CD3AD3D0F02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="18000" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="18000" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="396">
   <si>
     <t>Alphabet valuation teaching model</t>
   </si>
@@ -150,6 +150,12 @@
     <t>https://www.sec.gov/Archives/edgar/data/1018724/000101872426000026/amzn-20260630.htm</t>
   </si>
   <si>
+    <t>S10 — Meta Q2 2026 10-Q, June 30 balance sheet, Class A and B shares outstanding</t>
+  </si>
+  <si>
+    <t>https://www.sec.gov/Archives/edgar/data/1326801/000162828026050705/meta-20260630.htm</t>
+  </si>
+  <si>
     <t>Q1 — GOOGL closing quote, October 16, 2026, Google Finance vendor display</t>
   </si>
   <si>
@@ -501,7 +507,10 @@
     <t>Required / modeled terminal FCF</t>
   </si>
   <si>
-    <t>DCF bounds: WACC ±1.5 percentage points and growth ±0.5 points, for the selected operating case.</t>
+    <t>Terminal-value condition</t>
+  </si>
+  <si>
+    <t>DCF low/high: WACC ±1.5 pp, growth ±0.5 pp. Peer low/high: minimum/maximum multiples. These are not Bull/Bear cases.</t>
   </si>
   <si>
     <t>Forward P/E uses CY2027 adjusted consensus, with MSFT calendarized. GAAP P/E includes investment gains.</t>
@@ -936,7 +945,7 @@
     <t>Sensitivity</t>
   </si>
   <si>
-    <t>WACC rows and perpetual growth columns. Same selected operating case; normalized terminal capex in every cell.</t>
+    <t>Same operating case. Rows vary WACC; columns vary growth. #N/A marks invalid WACC ≤ growth.</t>
   </si>
   <si>
     <t>WACC / terminal growth</t>
@@ -972,10 +981,10 @@
     <t>Quotes 2026-10-16; financials TTM through 2026-06-30. USD millions.</t>
   </si>
   <si>
-    <t>Q1 / Q2 / Q3 / Q4. Google Finance vendor displays; exchange-direct unavailable.</t>
-  </si>
-  <si>
-    <t>S2 all Alphabet classes; S4 Microsoft period end; S5 Meta Q2 basic weighted-average proxy; S7 Amazon period end.</t>
+    <t>GOOGL linked to Assumptions!D7. Q2 / Q3 / Q4 vendor closes 2026-10-16; exchange-direct unavailable.</t>
+  </si>
+  <si>
+    <t>GOOGL linked to Historicals!H47; S4 Microsoft period end; S10 Meta Class A + B (rows 68–69); S7 Amazon period end.</t>
   </si>
   <si>
     <t>Equity market value proxy</t>
@@ -1159,6 +1168,15 @@
   </si>
   <si>
     <t>EV excludes leases for all. EBITD retains intangible amortization expense; no SBC, content, operating-lease or other cash-flow addbacks.</t>
+  </si>
+  <si>
+    <t>META Class A, period-end shares</t>
+  </si>
+  <si>
+    <t>S10: June 30, 2026 balance sheet, shares in millions.</t>
+  </si>
+  <si>
+    <t>META Class B, period-end shares</t>
   </si>
   <si>
     <t>Forward earnings inputs</t>
@@ -1326,7 +1344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1377,6 +1395,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1429,7 +1448,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:rPr sz="975">
+              <a:rPr lang="en-US" sz="975">
                 <a:latin typeface="Arial"/>
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
@@ -1488,10 +1507,10 @@
                   <c:v>212.65234753731744</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>528.72437643248361</c:v>
+                  <c:v>529.76394461264977</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>293.83206968582164</c:v>
+                  <c:v>294.39855027187718</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>273.29739170927058</c:v>
@@ -1504,7 +1523,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2E65-45F9-A382-6F68BF58A694}"/>
+              <c16:uniqueId val="{00000000-753E-4297-88F6-2A7F2E61AB93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1564,7 +1583,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2E65-45F9-A382-6F68BF58A694}"/>
+              <c16:uniqueId val="{00000001-753E-4297-88F6-2A7F2E61AB93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3549,12 +3568,14 @@
     <row r="106" spans="1:12" ht="19" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
+      <c r="C106" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D106" s="45"/>
+      <c r="E106" s="45"/>
+      <c r="F106" s="45"/>
+      <c r="G106" s="45"/>
+      <c r="H106" s="45"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
@@ -3563,14 +3584,16 @@
     <row r="107" spans="1:12" ht="19" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
+      <c r="C107" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="D107" s="45"/>
+      <c r="E107" s="45"/>
+      <c r="F107" s="45"/>
+      <c r="G107" s="45"/>
+      <c r="H107" s="45"/>
+      <c r="I107" s="44"/>
+      <c r="J107" s="44"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
     </row>
@@ -4737,11 +4760,13 @@
       <c r="L190" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="61">
+    <mergeCell ref="C107:J107"/>
     <mergeCell ref="C100:H100"/>
     <mergeCell ref="C101:J101"/>
     <mergeCell ref="C103:H103"/>
     <mergeCell ref="C104:J104"/>
+    <mergeCell ref="C106:H106"/>
     <mergeCell ref="C92:J92"/>
     <mergeCell ref="C94:H94"/>
     <mergeCell ref="C95:J95"/>
@@ -4835,7 +4860,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -4879,7 +4904,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -4902,7 +4927,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="19">
         <v>46312</v>
@@ -4913,7 +4938,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -4922,7 +4947,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D7" s="20">
         <v>340.59</v>
@@ -4933,7 +4958,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -4942,7 +4967,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D8" s="19">
         <v>46311</v>
@@ -4953,7 +4978,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -4962,7 +4987,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" s="21">
         <v>4.4999999999999998E-2</v>
@@ -4973,7 +4998,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -4982,7 +5007,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10" s="22">
         <v>1.2</v>
@@ -4993,7 +5018,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -5002,7 +5027,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D11" s="21">
         <v>4.4999999999999998E-2</v>
@@ -5013,7 +5038,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -5022,7 +5047,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" s="21">
         <v>4.8000000000000001E-2</v>
@@ -5033,7 +5058,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -5042,7 +5067,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D13" s="21">
         <v>0.2</v>
@@ -5053,7 +5078,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -5062,7 +5087,7 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="21">
         <v>0.03</v>
@@ -5073,7 +5098,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -5082,7 +5107,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" s="22">
         <v>1.1499999999999999</v>
@@ -5093,7 +5118,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -5102,7 +5127,7 @@
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D16" s="21">
         <v>0</v>
@@ -5113,7 +5138,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -5122,7 +5147,7 @@
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" s="18">
         <v>195000</v>
@@ -5133,7 +5158,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -5142,7 +5167,7 @@
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" s="18">
         <v>205000</v>
@@ -5153,7 +5178,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -5162,7 +5187,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D19" s="2">
         <f>AVERAGE(D17:D18)</f>
@@ -5181,7 +5206,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D20" s="21">
         <v>6.25E-2</v>
@@ -5192,7 +5217,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -5201,7 +5226,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D21" s="21">
         <v>5.0000000000000001E-3</v>
@@ -5212,7 +5237,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -5221,7 +5246,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D22" s="21">
         <v>5.0000000000000001E-3</v>
@@ -5232,7 +5257,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -5241,7 +5266,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D23" s="18">
         <v>0</v>
@@ -5252,7 +5277,7 @@
       <c r="H23" s="2"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -5289,26 +5314,26 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -5331,7 +5356,7 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D28" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D29,D30,D31)),CHOOSE($D$4,D29,D30,D31),"Missing input")</f>
@@ -5355,7 +5380,7 @@
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -5364,7 +5389,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D29" s="21">
         <v>0.16</v>
@@ -5383,7 +5408,7 @@
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -5392,7 +5417,7 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D30" s="21">
         <v>0.19</v>
@@ -5411,7 +5436,7 @@
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -5420,7 +5445,7 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D31" s="21">
         <v>0.1</v>
@@ -5439,7 +5464,7 @@
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -5462,7 +5487,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D33" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D34,D35,D36)),CHOOSE($D$4,D34,D35,D36),"Missing input")</f>
@@ -5486,7 +5511,7 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -5495,7 +5520,7 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D34" s="21">
         <v>0.13</v>
@@ -5514,7 +5539,7 @@
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -5523,7 +5548,7 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D35" s="21">
         <v>0.16</v>
@@ -5542,7 +5567,7 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -5551,7 +5576,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D36" s="21">
         <v>0.08</v>
@@ -5570,7 +5595,7 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -5593,7 +5618,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D38" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D39,D40,D41)),CHOOSE($D$4,D39,D40,D41),"Missing input")</f>
@@ -5617,7 +5642,7 @@
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -5626,7 +5651,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D39" s="21">
         <v>-0.02</v>
@@ -5645,7 +5670,7 @@
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -5654,7 +5679,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D40" s="21">
         <v>0</v>
@@ -5673,7 +5698,7 @@
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -5682,7 +5707,7 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D41" s="21">
         <v>-0.05</v>
@@ -5701,7 +5726,7 @@
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -5724,7 +5749,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D43" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D44,D45,D46)),CHOOSE($D$4,D44,D45,D46),"Missing input")</f>
@@ -5748,7 +5773,7 @@
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -5757,7 +5782,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D44" s="21">
         <v>0.16</v>
@@ -5776,7 +5801,7 @@
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -5785,7 +5810,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D45" s="21">
         <v>0.2</v>
@@ -5804,7 +5829,7 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -5813,7 +5838,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D46" s="21">
         <v>0.1</v>
@@ -5832,7 +5857,7 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -5855,7 +5880,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D48" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D49,D50,D51)),CHOOSE($D$4,D49,D50,D51),"Missing input")</f>
@@ -5879,7 +5904,7 @@
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -5888,7 +5913,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D49" s="21">
         <v>0.7</v>
@@ -5907,7 +5932,7 @@
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -5916,7 +5941,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D50" s="21">
         <v>0.85</v>
@@ -5935,7 +5960,7 @@
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -5944,7 +5969,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D51" s="21">
         <v>0.45</v>
@@ -5963,7 +5988,7 @@
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -5986,7 +6011,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D53" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D54,D55,D56)),CHOOSE($D$4,D54,D55,D56),"Missing input")</f>
@@ -6010,7 +6035,7 @@
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -6019,7 +6044,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D54" s="21">
         <v>0.1</v>
@@ -6038,7 +6063,7 @@
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -6047,7 +6072,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D55" s="21">
         <v>0.2</v>
@@ -6066,7 +6091,7 @@
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -6075,7 +6100,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D56" s="21">
         <v>0</v>
@@ -6094,7 +6119,7 @@
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -6117,7 +6142,7 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D58" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D59,D60,D61)),CHOOSE($D$4,D59,D60,D61),"Missing input")</f>
@@ -6141,7 +6166,7 @@
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -6150,7 +6175,7 @@
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D59" s="21">
         <v>0.41</v>
@@ -6169,7 +6194,7 @@
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -6178,7 +6203,7 @@
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D60" s="21">
         <v>0.43</v>
@@ -6197,7 +6222,7 @@
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -6206,7 +6231,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D61" s="21">
         <v>0.38</v>
@@ -6225,7 +6250,7 @@
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -6248,7 +6273,7 @@
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D63" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D64,D65,D66)),CHOOSE($D$4,D64,D65,D66),"Missing input")</f>
@@ -6272,7 +6297,7 @@
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -6281,7 +6306,7 @@
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D64" s="21">
         <v>0.34</v>
@@ -6300,7 +6325,7 @@
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -6309,7 +6334,7 @@
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D65" s="21">
         <v>0.36</v>
@@ -6328,7 +6353,7 @@
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -6337,7 +6362,7 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D66" s="21">
         <v>0.28000000000000003</v>
@@ -6356,7 +6381,7 @@
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -6379,7 +6404,7 @@
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D68" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D69,D70,D71)),CHOOSE($D$4,D69,D70,D71),"Missing input")</f>
@@ -6403,7 +6428,7 @@
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -6412,7 +6437,7 @@
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D69" s="21">
         <v>-4.5</v>
@@ -6431,7 +6456,7 @@
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -6440,7 +6465,7 @@
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D70" s="21">
         <v>-4</v>
@@ -6459,7 +6484,7 @@
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -6468,7 +6493,7 @@
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D71" s="21">
         <v>-5</v>
@@ -6487,7 +6512,7 @@
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -6510,7 +6535,7 @@
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D73" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D74,D75,D76)),CHOOSE($D$4,D74,D75,D76),"Missing input")</f>
@@ -6534,7 +6559,7 @@
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -6543,7 +6568,7 @@
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D74" s="21">
         <v>0.05</v>
@@ -6562,7 +6587,7 @@
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -6571,7 +6596,7 @@
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D75" s="21">
         <v>4.4999999999999998E-2</v>
@@ -6590,7 +6615,7 @@
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -6599,7 +6624,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D76" s="21">
         <v>0.06</v>
@@ -6618,7 +6643,7 @@
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -6641,7 +6666,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D78" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D79,D80,D81)),CHOOSE($D$4,D79,D80,D81),"Missing input")</f>
@@ -6665,7 +6690,7 @@
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -6674,7 +6699,7 @@
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D79" s="21">
         <v>7.0000000000000007E-2</v>
@@ -6693,7 +6718,7 @@
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -6702,7 +6727,7 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D80" s="21">
         <v>6.5000000000000002E-2</v>
@@ -6721,7 +6746,7 @@
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -6730,7 +6755,7 @@
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D81" s="21">
         <v>0.08</v>
@@ -6749,7 +6774,7 @@
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -6772,10 +6797,10 @@
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E83" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,E84,E85,E86)),CHOOSE($D$4,E84,E85,E86),"Missing input")</f>
@@ -6795,7 +6820,7 @@
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -6804,7 +6829,7 @@
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D84" s="26"/>
       <c r="E84" s="21">
@@ -6821,7 +6846,7 @@
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -6830,7 +6855,7 @@
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D85" s="26"/>
       <c r="E85" s="21">
@@ -6847,7 +6872,7 @@
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -6856,7 +6881,7 @@
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D86" s="26"/>
       <c r="E86" s="21">
@@ -6873,7 +6898,7 @@
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -6896,7 +6921,7 @@
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D88" s="25">
         <f>IF(ISNUMBER(CHOOSE($D$4,D89,D90,D91)),CHOOSE($D$4,D89,D90,D91),"Missing input")</f>
@@ -6920,7 +6945,7 @@
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
@@ -6929,7 +6954,7 @@
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D89" s="21">
         <v>0.1</v>
@@ -6948,7 +6973,7 @@
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
@@ -6957,7 +6982,7 @@
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D90" s="21">
         <v>0.09</v>
@@ -6976,7 +7001,7 @@
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
@@ -6985,7 +7010,7 @@
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D91" s="21">
         <v>0.12</v>
@@ -7004,7 +7029,7 @@
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
@@ -8438,7 +8463,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -8501,7 +8526,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="31">
         <f>Assumptions!D6</f>
@@ -8509,7 +8534,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G6" s="36">
         <f>Assumptions!D7</f>
@@ -8539,19 +8564,19 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
@@ -8563,7 +8588,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D9" s="41">
         <f>Sensitivity!E16</f>
@@ -8591,7 +8616,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" s="36">
         <f>Multiples!D59</f>
@@ -8599,7 +8624,7 @@
       </c>
       <c r="E10" s="36">
         <f>Multiples!E59</f>
-        <v>528.72437643248361</v>
+        <v>529.76394461264977</v>
       </c>
       <c r="F10" s="36">
         <f>Multiples!F59</f>
@@ -8619,7 +8644,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D11" s="36">
         <f>Multiples!D60</f>
@@ -8627,7 +8652,7 @@
       </c>
       <c r="E11" s="36">
         <f>Multiples!E60</f>
-        <v>293.83206968582164</v>
+        <v>294.39855027187718</v>
       </c>
       <c r="F11" s="36">
         <f>Multiples!F60</f>
@@ -8647,11 +8672,11 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D12" s="36">
         <f>Multiples!D61</f>
-        <v>240.95073684765467</v>
+        <v>241.41286152545865</v>
       </c>
       <c r="E12" s="36">
         <f>Multiples!E61</f>
@@ -8675,7 +8700,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D13" s="36">
         <f>Multiples!D62</f>
@@ -8717,7 +8742,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D15" s="28">
         <f>DCF!D15</f>
@@ -8736,7 +8761,7 @@
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" s="28">
         <f>Assumptions!D14</f>
@@ -8755,7 +8780,7 @@
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D17" s="28">
         <f>DCF!D40</f>
@@ -8774,7 +8799,7 @@
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D18" s="28">
         <f>DCF!D52</f>
@@ -8807,7 +8832,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D20" s="5">
         <f>Projections!H15</f>
@@ -8826,7 +8851,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D21" s="28">
         <f>Assumptions!E83</f>
@@ -8845,7 +8870,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D22" s="5">
         <f>Projections!E40</f>
@@ -8864,7 +8889,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="38">
         <f>Sensitivity!D23</f>
@@ -8882,12 +8907,17 @@
     <row r="24" spans="1:12" ht="19" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="C24" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="46" t="str">
+        <f>IF(DCF!D15&lt;=Assumptions!D14,"Growth must be below WACC","WACC exceeds growth")</f>
+        <v>WACC exceeds growth</v>
+      </c>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -8911,7 +8941,7 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="42" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D26" s="43"/>
       <c r="E26" s="43"/>
@@ -8941,7 +8971,7 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="42" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D28" s="43"/>
       <c r="E28" s="43"/>
@@ -8971,7 +9001,7 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="42" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D30" s="43"/>
       <c r="E30" s="43"/>
@@ -11224,10 +11254,11 @@
       <c r="L190" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="C28:J28"/>
     <mergeCell ref="C30:J30"/>
+    <mergeCell ref="D24:H24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11267,7 +11298,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -11330,26 +11361,26 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -11372,7 +11403,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D8" s="11">
         <v>175033</v>
@@ -11391,7 +11422,7 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -11400,7 +11431,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D9" s="11">
         <v>31510</v>
@@ -11419,7 +11450,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -11428,7 +11459,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D10" s="11">
         <v>31312</v>
@@ -11447,7 +11478,7 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -11456,7 +11487,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D11" s="11">
         <v>34688</v>
@@ -11475,7 +11506,7 @@
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -11484,7 +11515,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D12" s="11">
         <v>33088</v>
@@ -11503,7 +11534,7 @@
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -11512,7 +11543,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D13" s="11">
         <v>1527</v>
@@ -11531,7 +11562,7 @@
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -11540,7 +11571,7 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D14" s="11">
         <v>236</v>
@@ -11559,7 +11590,7 @@
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -11568,7 +11599,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D15" s="15">
         <v>307394</v>
@@ -11587,7 +11618,7 @@
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -11596,7 +11627,7 @@
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D16" s="13">
         <f>SUM(D8:D14)-D15</f>
@@ -11641,7 +11672,7 @@
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D18" s="11">
         <v>133332</v>
@@ -11660,7 +11691,7 @@
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -11669,7 +11700,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D19" s="11">
         <v>45427</v>
@@ -11688,7 +11719,7 @@
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -11697,7 +11728,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D20" s="11">
         <v>27917</v>
@@ -11716,7 +11747,7 @@
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -11725,7 +11756,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D21" s="11">
         <v>16425</v>
@@ -11744,7 +11775,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -11753,7 +11784,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D22" s="15">
         <v>84293</v>
@@ -11772,7 +11803,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -11781,7 +11812,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D23" s="16">
         <f>D15-SUM(D18:D21)</f>
@@ -11812,7 +11843,7 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D24" s="13">
         <f>D23-D22</f>
@@ -11843,7 +11874,7 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D25" s="11">
         <v>85717</v>
@@ -11862,7 +11893,7 @@
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -11871,7 +11902,7 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D26" s="11">
         <v>11922</v>
@@ -11890,7 +11921,7 @@
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -11899,7 +11930,7 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="14" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D27" s="15">
         <v>73795</v>
@@ -11918,7 +11949,7 @@
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -11927,7 +11958,7 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D28" s="11">
         <v>73795</v>
@@ -11946,7 +11977,7 @@
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -11955,7 +11986,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D29" s="12">
         <v>5.8</v>
@@ -11974,7 +12005,7 @@
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -11983,7 +12014,7 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D30" s="11">
         <v>11946</v>
@@ -12002,7 +12033,7 @@
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -12011,7 +12042,7 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D31" s="11">
         <v>22460</v>
@@ -12030,7 +12061,7 @@
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -12039,7 +12070,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D32" s="11">
         <v>101746</v>
@@ -12058,7 +12089,7 @@
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -12067,7 +12098,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D33" s="11">
         <v>32251</v>
@@ -12086,7 +12117,7 @@
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -12095,7 +12126,7 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D34" s="16">
         <f>D32-D33</f>
@@ -12140,7 +12171,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -12153,7 +12184,7 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -12162,7 +12193,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -12175,7 +12206,7 @@
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -12184,7 +12215,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -12197,7 +12228,7 @@
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -12206,7 +12237,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -12219,7 +12250,7 @@
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -12228,7 +12259,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
@@ -12264,7 +12295,7 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -12277,7 +12308,7 @@
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -12286,7 +12317,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -12299,7 +12330,7 @@
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -12308,7 +12339,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -12321,7 +12352,7 @@
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -12330,7 +12361,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -12343,7 +12374,7 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -12352,7 +12383,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -12365,7 +12396,7 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -12374,7 +12405,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -12387,7 +12418,7 @@
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -12396,7 +12427,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -12409,7 +12440,7 @@
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -12418,7 +12449,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -12429,7 +12460,7 @@
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -12438,7 +12469,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -12451,7 +12482,7 @@
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -12460,7 +12491,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -12473,7 +12504,7 @@
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -12482,7 +12513,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -12493,7 +12524,7 @@
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -12502,7 +12533,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -12515,7 +12546,7 @@
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -12524,7 +12555,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -12535,7 +12566,7 @@
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -14492,7 +14523,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -14555,22 +14586,22 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -14595,7 +14626,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D8" s="5">
         <f>Historicals!H8+(Historicals!F8-Historicals!G8)*(1+Assumptions!D28)</f>
@@ -14626,7 +14657,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D9" s="5">
         <f>Historicals!H9+(Historicals!F9-Historicals!G9)*(1+Assumptions!D33)</f>
@@ -14657,7 +14688,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D10" s="5">
         <f>Historicals!H10+(Historicals!F10-Historicals!G10)*(1+Assumptions!D38)</f>
@@ -14688,7 +14719,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D11" s="5">
         <f>Historicals!H11+(Historicals!F11-Historicals!G11)*(1+Assumptions!D43)</f>
@@ -14719,7 +14750,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D12" s="5">
         <f>Historicals!H12+(Historicals!F12-Historicals!G12)*(1+Assumptions!D48)</f>
@@ -14750,7 +14781,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D13" s="5">
         <f>Historicals!H13+(Historicals!F13-Historicals!G13)*(1+Assumptions!D53)</f>
@@ -14781,7 +14812,7 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D14" s="5">
         <f>Historicals!H14+Assumptions!$D$23</f>
@@ -14812,7 +14843,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D15" s="16">
         <f>SUM(D8:D14)</f>
@@ -14885,7 +14916,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D19" s="5">
         <f>D8*Assumptions!D58</f>
@@ -14916,7 +14947,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D20" s="5">
         <f>D9*Assumptions!D58</f>
@@ -14947,7 +14978,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D21" s="5">
         <f>D10*Assumptions!D58</f>
@@ -14978,7 +15009,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D22" s="5">
         <f>D11*Assumptions!D58</f>
@@ -15009,7 +15040,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D23" s="5">
         <f>D12*Assumptions!D63</f>
@@ -15040,7 +15071,7 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D24" s="5">
         <f>D13*Assumptions!D68</f>
@@ -15071,7 +15102,7 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D25" s="5">
         <f>-D15*Assumptions!D73</f>
@@ -15102,7 +15133,7 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D26" s="16">
         <f>SUM(D19:D25)</f>
@@ -15133,7 +15164,7 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D27" s="23">
         <f>D26/D15</f>
@@ -15178,7 +15209,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D29" s="5">
         <f>D26*Assumptions!$D$13</f>
@@ -15209,7 +15240,7 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D30" s="16">
         <f>D26-D29</f>
@@ -15254,7 +15285,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D32" s="5">
         <f>D15*Assumptions!D78</f>
@@ -15285,7 +15316,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D33" s="5">
         <f>Assumptions!$D$19</f>
@@ -15316,7 +15347,7 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D34" s="23">
         <f>D33/D15</f>
@@ -15361,7 +15392,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D36" s="5">
         <f>D15*Assumptions!D88</f>
@@ -15392,7 +15423,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D37" s="5">
         <f>Historicals!F40</f>
@@ -15423,7 +15454,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D38" s="2">
         <f>D36-D37</f>
@@ -15468,7 +15499,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="14" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D40" s="16">
         <f>D30+D32-D33-D38</f>
@@ -15499,7 +15530,7 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D41" s="16">
         <f>D26+D32</f>
@@ -15544,7 +15575,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D43" s="43"/>
       <c r="E43" s="43"/>
@@ -15588,7 +15619,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
@@ -15604,7 +15635,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D47" s="23">
         <f>D8/SUM(D$8:D$13)</f>
@@ -15635,7 +15666,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D48" s="2">
         <f>D$32*D47</f>
@@ -15666,7 +15697,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D49" s="2">
         <f>D$33*D47</f>
@@ -15697,7 +15728,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D50" s="2">
         <f>D$38*D47</f>
@@ -15728,7 +15759,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D51" s="5">
         <f>D19*(1-Assumptions!$D$13)+D48-D49-D50</f>
@@ -15773,7 +15804,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
@@ -15789,7 +15820,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D54" s="23">
         <f>D9/SUM(D$8:D$13)</f>
@@ -15820,7 +15851,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D55" s="2">
         <f>D$32*D54</f>
@@ -15851,7 +15882,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D56" s="2">
         <f>D$33*D54</f>
@@ -15882,7 +15913,7 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D57" s="2">
         <f>D$38*D54</f>
@@ -15913,7 +15944,7 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D58" s="5">
         <f>D20*(1-Assumptions!$D$13)+D55-D56-D57</f>
@@ -15958,7 +15989,7 @@
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
@@ -15974,7 +16005,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D61" s="23">
         <f>D10/SUM(D$8:D$13)</f>
@@ -16005,7 +16036,7 @@
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D62" s="2">
         <f>D$32*D61</f>
@@ -16036,7 +16067,7 @@
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D63" s="2">
         <f>D$33*D61</f>
@@ -16067,7 +16098,7 @@
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D64" s="2">
         <f>D$38*D61</f>
@@ -16098,7 +16129,7 @@
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D65" s="5">
         <f>D21*(1-Assumptions!$D$13)+D62-D63-D64</f>
@@ -16143,7 +16174,7 @@
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -16159,7 +16190,7 @@
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D68" s="23">
         <f>D11/SUM(D$8:D$13)</f>
@@ -16190,7 +16221,7 @@
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D69" s="2">
         <f>D$32*D68</f>
@@ -16221,7 +16252,7 @@
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D70" s="2">
         <f>D$33*D68</f>
@@ -16252,7 +16283,7 @@
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D71" s="2">
         <f>D$38*D68</f>
@@ -16283,7 +16314,7 @@
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D72" s="5">
         <f>D22*(1-Assumptions!$D$13)+D69-D70-D71</f>
@@ -16328,7 +16359,7 @@
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
@@ -16344,7 +16375,7 @@
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D75" s="23">
         <f>D12/SUM(D$8:D$13)</f>
@@ -16375,7 +16406,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D76" s="2">
         <f>D$32*D75</f>
@@ -16406,7 +16437,7 @@
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D77" s="2">
         <f>D$33*D75</f>
@@ -16437,7 +16468,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D78" s="2">
         <f>D$38*D75</f>
@@ -16468,7 +16499,7 @@
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D79" s="5">
         <f>D23*(1-Assumptions!$D$13)+D76-D77-D78</f>
@@ -16513,7 +16544,7 @@
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
@@ -16529,7 +16560,7 @@
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D82" s="23">
         <f>D13/SUM(D$8:D$13)</f>
@@ -16560,7 +16591,7 @@
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D83" s="2">
         <f>D$32*D82</f>
@@ -16591,7 +16622,7 @@
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D84" s="2">
         <f>D$33*D82</f>
@@ -16622,7 +16653,7 @@
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D85" s="2">
         <f>D$38*D82</f>
@@ -16653,7 +16684,7 @@
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D86" s="5">
         <f>D24*(1-Assumptions!$D$13)+D83-D84-D85</f>
@@ -16726,7 +16757,7 @@
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D90" s="27">
         <f>SUM(D51,D58,D65,D72,D79,D86)+D25*(1-Assumptions!$D$13)-D40</f>
@@ -16785,7 +16816,7 @@
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
@@ -16801,7 +16832,7 @@
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D94" s="5">
         <f>Historicals!H22*(1-Assumptions!$D$13)</f>
@@ -16820,7 +16851,7 @@
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D95" s="5">
         <f>SUM(Historicals!H30,Historicals!H53)</f>
@@ -16839,7 +16870,7 @@
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D96" s="5">
         <f>Historicals!H33</f>
@@ -16858,7 +16889,7 @@
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D97" s="5">
         <f>Historicals!H40-Historicals!F40</f>
@@ -16877,7 +16908,7 @@
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D98" s="2">
         <f>D94+D95-D96-D97</f>
@@ -16896,7 +16927,7 @@
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D99" s="2">
         <f>D40-D98</f>
@@ -16929,7 +16960,7 @@
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="42" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D101" s="43"/>
       <c r="E101" s="43"/>
@@ -18229,7 +18260,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -18292,7 +18323,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D6" s="5">
         <f>Assumptions!D7*Historicals!H47</f>
@@ -18311,7 +18342,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D7" s="5">
         <f>SUM(Historicals!H45:H46)</f>
@@ -18330,7 +18361,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D8" s="5">
         <f>Historicals!H48*Historicals!H49</f>
@@ -18349,7 +18380,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D9" s="28">
         <f>Assumptions!D9+Assumptions!D10*Assumptions!D11</f>
@@ -18368,7 +18399,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D10" s="28">
         <f>Assumptions!D12*(1-Assumptions!D13)</f>
@@ -18387,7 +18418,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D11" s="28">
         <f>Assumptions!D20</f>
@@ -18406,7 +18437,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D12" s="23">
         <f>D6/SUM(D6:D8)</f>
@@ -18425,7 +18456,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D13" s="23">
         <f>D7/SUM(D6:D8)</f>
@@ -18444,7 +18475,7 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D14" s="23">
         <f>D8/SUM(D6:D8)</f>
@@ -18463,7 +18494,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D15" s="25">
         <f>SUMPRODUCT(D9:D11,D12:D14)</f>
@@ -18496,22 +18527,22 @@
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -18522,7 +18553,7 @@
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D18" s="30">
         <v>46388</v>
@@ -18548,7 +18579,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D19" s="31">
         <f>Assumptions!D6</f>
@@ -18579,7 +18610,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D20" s="33">
         <f>(D18-D19)/365</f>
@@ -18610,7 +18641,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D21" s="34">
         <f>((D18+D19)/2-Assumptions!D6)/365</f>
@@ -18641,7 +18672,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D22" s="5">
         <f>Projections!D40</f>
@@ -18672,7 +18703,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D23" s="5">
         <f>Projections!D99*(D18-D19)/(D18-DATE(2026,7,1))</f>
@@ -18703,7 +18734,7 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D24" s="33">
         <f>1/(1+$D$15)^D21</f>
@@ -18734,7 +18765,7 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D25" s="16">
         <f>D23*D24</f>
@@ -18807,7 +18838,7 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D29" s="5">
         <f>Projections!H15*(1+Assumptions!D14)</f>
@@ -18826,7 +18857,7 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D30" s="5">
         <f>Projections!H30*(1+Assumptions!D14)</f>
@@ -18845,7 +18876,7 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D31" s="5">
         <f>Projections!H32*(1+Assumptions!D14)</f>
@@ -18864,7 +18895,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D32" s="5">
         <f>D31*Assumptions!D15</f>
@@ -18883,7 +18914,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D33" s="5">
         <f>Projections!H36*Assumptions!D14</f>
@@ -18902,7 +18933,7 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D34" s="16">
         <f>D30+D31-D32-D33</f>
@@ -18921,10 +18952,10 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D35" s="5">
-        <f>D34/(D15-Assumptions!D14)</f>
+        <f>IF(D15&lt;=Assumptions!D14,NA(),D34/(D15-Assumptions!D14))</f>
         <v>3502295.6590318307</v>
       </c>
       <c r="E35" s="2"/>
@@ -18940,7 +18971,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D36" s="34">
         <f>(H18-Assumptions!D6)/365</f>
@@ -18959,7 +18990,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D37" s="2">
         <f>D35/(1+D15)^D36</f>
@@ -18978,7 +19009,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(D25:H25)</f>
@@ -18997,7 +19028,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D39" s="16">
         <f>SUM(D37:D38)</f>
@@ -19016,7 +19047,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D40" s="23">
         <f>D37/D39</f>
@@ -19049,7 +19080,7 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D42" s="5">
         <f>Historicals!H42</f>
@@ -19068,7 +19099,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D43" s="5">
         <f>-SUM(Historicals!H43:H44)</f>
@@ -19087,7 +19118,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D44" s="2">
         <f>-D8</f>
@@ -19106,7 +19137,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D45" s="5">
         <f>Historicals!H50*Assumptions!D16</f>
@@ -19125,7 +19156,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D46" s="5">
         <f>-Historicals!H51</f>
@@ -19144,7 +19175,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D47" s="5">
         <f>-Historicals!H52</f>
@@ -19163,7 +19194,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D48" s="16">
         <f>SUM(D42:D47)</f>
@@ -19182,7 +19213,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D49" s="16">
         <f>D39+D48</f>
@@ -19201,7 +19232,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D50" s="5">
         <f>Historicals!H47</f>
@@ -19220,7 +19251,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D51" s="35">
         <f>D49/D50</f>
@@ -19239,7 +19270,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D52" s="28">
         <f>D51/Assumptions!D7-1</f>
@@ -19286,7 +19317,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="42" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D55" s="43"/>
       <c r="E55" s="43"/>
@@ -21229,7 +21260,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -21292,15 +21323,15 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="42" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D6" s="43"/>
       <c r="E6" s="43"/>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
       <c r="H6" s="43"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
@@ -21336,7 +21367,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D9" s="28">
         <f>Assumptions!D14+(0-2)*Assumptions!D22</f>
@@ -21371,23 +21402,23 @@
         <v>8.2468733664970012E-2</v>
       </c>
       <c r="D10" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C10-D$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C10&lt;=D$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C10-D$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>240.06417659870931</v>
       </c>
       <c r="E10" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C10-E$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C10&lt;=E$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C10-E$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>259.95483242233149</v>
       </c>
       <c r="F10" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C10-F$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C10&lt;=F$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C10-F$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>283.63644229310694</v>
       </c>
       <c r="G10" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C10-G$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C10&lt;=G$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C10-G$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>312.30693811940796</v>
       </c>
       <c r="H10" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C10-H$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C10&lt;=H$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C10)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C10-H$9)/(1+$C10)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>347.7283995036837</v>
       </c>
       <c r="I10" s="1"/>
@@ -21403,23 +21434,23 @@
         <v>8.7468733664970016E-2</v>
       </c>
       <c r="D11" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C11-D$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C11&lt;=D$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C11-D$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>219.55791707558728</v>
       </c>
       <c r="E11" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C11-E$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C11&lt;=E$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C11-E$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>236.22388083245849</v>
       </c>
       <c r="F11" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C11-F$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C11&lt;=F$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C11-F$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>255.78984998252847</v>
       </c>
       <c r="G11" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C11-G$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C11&lt;=G$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C11-G$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>279.08489124533611</v>
       </c>
       <c r="H11" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C11-H$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C11&lt;=H$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C11)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C11-H$9)/(1+$C11)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>307.28738199420377</v>
       </c>
       <c r="I11" s="1"/>
@@ -21435,23 +21466,23 @@
         <v>9.2468733664970007E-2</v>
       </c>
       <c r="D12" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C12-D$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C12&lt;=D$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C12-D$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>201.93593936961719</v>
       </c>
       <c r="E12" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C12-E$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C12&lt;=E$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C12-E$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>216.06878526818957</v>
       </c>
       <c r="F12" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C12-F$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C12&lt;=F$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C12-F$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>232.46401829539656</v>
       </c>
       <c r="G12" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C12-G$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C12&lt;=G$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C12-G$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>251.71214749442234</v>
       </c>
       <c r="H12" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C12-H$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C12&lt;=H$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C12)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C12-H$9)/(1+$C12)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>274.62877178653196</v>
       </c>
       <c r="I12" s="1"/>
@@ -21467,23 +21498,23 @@
         <v>9.7468733664970011E-2</v>
       </c>
       <c r="D13" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C13-D$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C13&lt;=D$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C13-D$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>186.63844173385544</v>
       </c>
       <c r="E13" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C13-E$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C13&lt;=E$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C13-E$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>198.74797638057288</v>
       </c>
       <c r="F13" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C13-F$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C13&lt;=F$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C13-F$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>212.65234753731741</v>
       </c>
       <c r="G13" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C13-G$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C13&lt;=G$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C13-G$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>228.78253156731711</v>
       </c>
       <c r="H13" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C13-H$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C13&lt;=H$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C13)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C13-H$9)/(1+$C13)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>247.71949121273855</v>
       </c>
       <c r="I13" s="1"/>
@@ -21499,23 +21530,23 @@
         <v>0.10246873366497002</v>
       </c>
       <c r="D14" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C14-D$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C14&lt;=D$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C14-D$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>173.2414230528191</v>
       </c>
       <c r="E14" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C14-E$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C14&lt;=E$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C14-E$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>183.71137698331498</v>
       </c>
       <c r="F14" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C14-F$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C14&lt;=F$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C14-F$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>195.6260855550193</v>
       </c>
       <c r="G14" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C14-G$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C14&lt;=G$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C14-G$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>209.30675413878919</v>
       </c>
       <c r="H14" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C14-H$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C14&lt;=H$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C14)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C14-H$9)/(1+$C14)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>225.17742526961604</v>
       </c>
       <c r="I14" s="1"/>
@@ -21531,23 +21562,23 @@
         <v>0.10746873366497001</v>
       </c>
       <c r="D15" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C15-D$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C15&lt;=D$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C15-D$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>161.41786741439796</v>
       </c>
       <c r="E15" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C15-E$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C15&lt;=E$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C15-E$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>170.54235066326609</v>
       </c>
       <c r="F15" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C15-F$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C15&lt;=F$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C15-F$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>180.84466176825094</v>
       </c>
       <c r="G15" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C15-G$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C15&lt;=G$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C15-G$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>192.56859438971111</v>
       </c>
       <c r="H15" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C15-H$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C15&lt;=H$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C15)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C15-H$9)/(1+$C15)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>206.03021082182028</v>
       </c>
       <c r="I15" s="1"/>
@@ -21563,23 +21594,23 @@
         <v>0.11246873366497001</v>
       </c>
       <c r="D16" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C16-D$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C16&lt;=D$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+D$9)-Projections!$H$36*D$9)/($C16-D$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>150.91152178004901</v>
       </c>
       <c r="E16" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C16-E$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C16&lt;=E$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+E$9)-Projections!$H$36*E$9)/($C16-E$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>158.91956089630858</v>
       </c>
       <c r="F16" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C16-F$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C16&lt;=F$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+F$9)-Projections!$H$36*F$9)/($C16-F$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>167.89863943082722</v>
       </c>
       <c r="G16" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C16-G$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C16&lt;=G$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+G$9)-Projections!$H$36*G$9)/($C16-G$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>178.03677635054555</v>
       </c>
       <c r="H16" s="36">
-        <f>(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C16-H$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50</f>
+        <f>IF($C16&lt;=H$9,NA(),(SUMPRODUCT(DCF!$D$23:$H$23,1/(1+$C16)^DCF!$D$21:$H$21)+((Projections!$H$30+Projections!$H$32*(1-Assumptions!$D$15))*(1+H$9)-Projections!$H$36*H$9)/($C16-H$9)/(1+$C16)^DCF!$D$36+DCF!$D$48)/DCF!$D$50)</f>
         <v>189.57388030156156</v>
       </c>
       <c r="I16" s="1"/>
@@ -21619,7 +21650,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D19" s="37">
         <f>F13-DCF!D51</f>
@@ -21652,7 +21683,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D21" s="36">
         <f>Assumptions!D7</f>
@@ -21671,7 +21702,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D22" s="5">
         <f>(Assumptions!D7*DCF!D50-DCF!D48-DCF!D38)*(1+DCF!D15)^DCF!D36*(DCF!D15-Assumptions!D14)</f>
@@ -21690,7 +21721,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="38">
         <f>D22/DCF!D34</f>
@@ -24045,7 +24076,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C6:H6"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:H16">
     <cfRule type="colorScale" priority="1">
@@ -24096,7 +24127,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -24159,24 +24190,24 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -24199,9 +24230,10 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="39">
+        <v>137</v>
+      </c>
+      <c r="D8" s="36">
+        <f>Assumptions!D7</f>
         <v>340.59</v>
       </c>
       <c r="E8" s="39">
@@ -24216,7 +24248,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -24225,16 +24257,18 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D9" s="11">
+        <v>297</v>
+      </c>
+      <c r="D9" s="5">
+        <f>Historicals!H47</f>
         <v>12230</v>
       </c>
       <c r="E9" s="11">
         <v>7427</v>
       </c>
-      <c r="F9" s="11">
-        <v>2543</v>
+      <c r="F9" s="2">
+        <f>SUM(F68:F69)</f>
+        <v>2548</v>
       </c>
       <c r="G9" s="11">
         <v>10783</v>
@@ -24242,7 +24276,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -24251,7 +24285,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D10" s="2">
         <f>D8*D9</f>
@@ -24263,7 +24297,7 @@
       </c>
       <c r="F10" s="2">
         <f>F8*F9</f>
-        <v>1803800.7600000002</v>
+        <v>1807347.36</v>
       </c>
       <c r="G10" s="2">
         <f>G8*G9</f>
@@ -24279,7 +24313,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D11" s="11">
         <v>55911</v>
@@ -24296,7 +24330,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -24305,7 +24339,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D12" s="11">
         <v>186563</v>
@@ -24322,7 +24356,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -24331,7 +24365,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D13" s="11">
         <v>98165</v>
@@ -24348,7 +24382,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -24357,7 +24391,7 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D14" s="11">
         <v>1999</v>
@@ -24374,7 +24408,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -24383,7 +24417,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D15" s="11">
         <v>19250</v>
@@ -24400,7 +24434,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -24409,7 +24443,7 @@
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D16" s="2">
         <f>D10+SUM(D13:D15)-SUM(D11:D12)</f>
@@ -24421,7 +24455,7 @@
       </c>
       <c r="F16" s="2">
         <f>F10+SUM(F13:F15)-SUM(F11:F12)</f>
-        <v>1797204.7600000002</v>
+        <v>1800751.36</v>
       </c>
       <c r="G16" s="2">
         <f>G10+SUM(G13:G15)-SUM(G11:G12)</f>
@@ -24479,7 +24513,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D20" s="11">
         <v>402836</v>
@@ -24494,7 +24528,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -24503,7 +24537,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D21" s="11">
         <v>186662</v>
@@ -24518,7 +24552,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -24527,7 +24561,7 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D22" s="11">
         <v>229692</v>
@@ -24542,7 +24576,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -24551,7 +24585,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D23" s="2">
         <f>D20-D21+D22</f>
@@ -24593,7 +24627,7 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D25" s="11">
         <v>129039</v>
@@ -24608,7 +24642,7 @@
       <c r="H25" s="2"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -24617,7 +24651,7 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D26" s="11">
         <v>61877</v>
@@ -24632,7 +24666,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -24641,7 +24675,7 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D27" s="11">
         <v>80466</v>
@@ -24656,7 +24690,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -24665,7 +24699,7 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D28" s="2">
         <f>D25-D26+D27</f>
@@ -24707,7 +24741,7 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D30" s="11">
         <v>132170</v>
@@ -24722,7 +24756,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -24731,7 +24765,7 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D31" s="11">
         <v>62736</v>
@@ -24746,7 +24780,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -24755,7 +24789,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D32" s="11">
         <v>174685</v>
@@ -24770,7 +24804,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -24779,7 +24813,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D33" s="2">
         <f>D30-D31+D32</f>
@@ -24821,7 +24855,7 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D35" s="11">
         <v>21136</v>
@@ -24836,7 +24870,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -24845,7 +24879,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D36" s="11">
         <v>9485</v>
@@ -24860,7 +24894,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -24869,7 +24903,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D37" s="11">
         <v>13586</v>
@@ -24884,7 +24918,7 @@
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -24893,7 +24927,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D38" s="2">
         <f>D35-D36+D37</f>
@@ -24935,7 +24969,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="11">
@@ -24946,7 +24980,7 @@
       <c r="H40" s="2"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -24955,7 +24989,7 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
@@ -24966,7 +25000,7 @@
       <c r="H41" s="2"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -24975,7 +25009,7 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
@@ -24986,7 +25020,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -24995,7 +25029,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
@@ -25006,7 +25040,7 @@
       <c r="H43" s="2"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -25029,7 +25063,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D45" s="2">
         <f>D28+D38</f>
@@ -25050,7 +25084,7 @@
       <c r="H45" s="2"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -25073,7 +25107,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D47" s="40">
         <f>D10/D33</f>
@@ -25085,7 +25119,7 @@
       </c>
       <c r="F47" s="40">
         <f>F10/F33</f>
-        <v>26.488307439278689</v>
+        <v>26.540388263972513</v>
       </c>
       <c r="G47" s="40">
         <f>G10/G33</f>
@@ -25101,7 +25135,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D48" s="40">
         <f>D8/D77</f>
@@ -25122,7 +25156,7 @@
       <c r="H48" s="2"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -25131,7 +25165,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D49" s="40">
         <f>D16/D23</f>
@@ -25143,7 +25177,7 @@
       </c>
       <c r="F49" s="40">
         <f>F16/F23</f>
-        <v>7.8739469083931013</v>
+        <v>7.8894853382519816</v>
       </c>
       <c r="G49" s="40">
         <f>G16/G23</f>
@@ -25159,7 +25193,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D50" s="40">
         <f>D16/D45</f>
@@ -25171,7 +25205,7 @@
       </c>
       <c r="F50" s="40">
         <f>F16/F45</f>
-        <v>16.56776392934843</v>
+        <v>16.600458718979315</v>
       </c>
       <c r="G50" s="40">
         <f>G16/G45</f>
@@ -25215,22 +25249,22 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -25239,7 +25273,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D54" s="40">
         <f>MIN(E47:G47)</f>
@@ -25247,7 +25281,7 @@
       </c>
       <c r="E54" s="40">
         <f>MEDIAN(E47:G47)</f>
-        <v>26.488307439278689</v>
+        <v>26.540388263972513</v>
       </c>
       <c r="F54" s="40">
         <f>MAX(E47:G47)</f>
@@ -25264,7 +25298,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D55" s="40">
         <f>MIN(E49:G49)</f>
@@ -25272,7 +25306,7 @@
       </c>
       <c r="E55" s="40">
         <f>MEDIAN(E49:G49)</f>
-        <v>7.8739469083931013</v>
+        <v>7.8894853382519816</v>
       </c>
       <c r="F55" s="40">
         <f>MAX(E49:G49)</f>
@@ -25289,11 +25323,11 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D56" s="40">
         <f>MIN(E50:G50)</f>
-        <v>16.56776392934843</v>
+        <v>16.600458718979315</v>
       </c>
       <c r="E56" s="40">
         <f>MEDIAN(E50:G50)</f>
@@ -25314,7 +25348,7 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D57" s="40">
         <f>MIN(E48:G48)</f>
@@ -25353,7 +25387,7 @@
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D59" s="29">
         <f>D54*$D$33/$D$9</f>
@@ -25361,7 +25395,7 @@
       </c>
       <c r="E59" s="29">
         <f>E54*$D$33/$D$9</f>
-        <v>528.72437643248361</v>
+        <v>529.76394461264977</v>
       </c>
       <c r="F59" s="29">
         <f>F54*$D$33/$D$9</f>
@@ -25378,7 +25412,7 @@
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D60" s="36">
         <f>(D55*$D$23+DCF!$D$48)/$D$9</f>
@@ -25386,7 +25420,7 @@
       </c>
       <c r="E60" s="36">
         <f>(E55*$D$23+DCF!$D$48)/$D$9</f>
-        <v>293.83206968582164</v>
+        <v>294.39855027187718</v>
       </c>
       <c r="F60" s="36">
         <f>(F55*$D$23+DCF!$D$48)/$D$9</f>
@@ -25403,11 +25437,11 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D61" s="36">
         <f>(D56*$D$45+DCF!$D$48)/$D$9</f>
-        <v>240.95073684765467</v>
+        <v>241.41286152545865</v>
       </c>
       <c r="E61" s="36">
         <f>(E56*$D$45+DCF!$D$48)/$D$9</f>
@@ -25428,7 +25462,7 @@
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D62" s="29">
         <f>D57*$D$77</f>
@@ -25467,7 +25501,7 @@
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="42" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D64" s="43"/>
       <c r="E64" s="43"/>
@@ -25497,7 +25531,7 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="42" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D66" s="43"/>
       <c r="E66" s="43"/>
@@ -25526,28 +25560,40 @@
     <row r="68" spans="1:12" ht="19" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
+      <c r="C68" s="1" t="s">
+        <v>376</v>
+      </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
+      <c r="F68" s="11">
+        <v>2206</v>
+      </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>377</v>
+      </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
     </row>
     <row r="69" spans="1:12" ht="19" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
+      <c r="C69" s="1" t="s">
+        <v>378</v>
+      </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="F69" s="11">
+        <v>342</v>
+      </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="J69" s="1" t="s">
+        <v>377</v>
+      </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
     </row>
@@ -25583,24 +25629,24 @@
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="9" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -25609,7 +25655,7 @@
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D73" s="39">
         <v>15.25</v>
@@ -25633,7 +25679,7 @@
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D74" s="30">
         <v>46752</v>
@@ -25657,7 +25703,7 @@
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D75" s="29"/>
       <c r="E75" s="39">
@@ -25675,7 +25721,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D76" s="24">
         <v>1</v>
@@ -25699,7 +25745,7 @@
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="14" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D77" s="35">
         <f>D73</f>
@@ -25727,7 +25773,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D78" s="30">
         <v>46311</v>
@@ -25765,7 +25811,7 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="42" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D80" s="43"/>
       <c r="E80" s="43"/>
@@ -25795,7 +25841,7 @@
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="42" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="D82" s="43"/>
       <c r="E82" s="43"/>
@@ -25825,24 +25871,24 @@
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="9" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -25851,7 +25897,7 @@
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D85" s="2">
         <f>D28</f>
@@ -25879,7 +25925,7 @@
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D86" s="2">
         <f>D38</f>
@@ -25907,7 +25953,7 @@
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="14" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D87" s="16">
         <f>D85+D86</f>
@@ -25935,7 +25981,7 @@
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D88" s="40">
         <f>D16/D87</f>
@@ -25947,7 +25993,7 @@
       </c>
       <c r="F88" s="40">
         <f>F16/F87</f>
-        <v>16.56776392934843</v>
+        <v>16.600458718979315</v>
       </c>
       <c r="G88" s="40">
         <f>G16/G87</f>
@@ -25963,7 +26009,7 @@
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D89" s="2">
         <f>D45-D87</f>
@@ -26005,7 +26051,7 @@
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="42" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D91" s="43"/>
       <c r="E91" s="43"/>
@@ -26035,7 +26081,7 @@
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="42" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D93" s="43"/>
       <c r="E93" s="43"/>
@@ -26065,7 +26111,7 @@
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="42" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D95" s="43"/>
       <c r="E95" s="43"/>

--- a/demo-runs/2026-10-17/demo3_dcf_valuation/GOOGL_DCF_Valuation.xlsx
+++ b/demo-runs/2026-10-17/demo3_dcf_valuation/GOOGL_DCF_Valuation.xlsx
@@ -90,7 +90,7 @@
     <t>Forward P/E uses CY2027 adjusted consensus EPS dated Oct 16. Microsoft is calendarized from FY2027 / FY2028.</t>
   </si>
   <si>
-    <t>Teaching model, not investment advice. Market and scenario assumptions require presenter review.</t>
+    <t>Teaching model, not investment advice. Market and scenario assumptions are dated and uncertain.</t>
   </si>
   <si>
     <t>Sources (IDs also appear beside the inputs)</t>
@@ -180,7 +180,7 @@
     <t>https://www.google.com/finance/quote/AMZN:NASDAQ</t>
   </si>
   <si>
-    <t>A1 — Author teaching assumptions, October 17, 2026; not company guidance</t>
+    <t>A1 — Teaching assumptions, October 17, 2026; not company guidance</t>
   </si>
   <si>
     <t>valuation-notes.md</t>
@@ -1227,7 +1227,7 @@
     <t>No SBC, content, operating-lease asset or other cash-flow addbacks. EV excludes lease liabilities uniformly; lease mixes still differ.</t>
   </si>
   <si>
-    <t>Full TTM intangible amortization is not verified for GOOGL / AMZN. EBITD replaces EBITDA by the presenter’s choice; it is not EBITDA.</t>
+    <t>Full TTM intangible amortization is unavailable for GOOGL / AMZN. EBITD adds PP&amp;E depreciation; intangible amortization stays expensed.</t>
   </si>
 </sst>
 </file>
